--- a/artfynd/A 25436-2023 artfynd.xlsx
+++ b/artfynd/A 25436-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25436-2023 artfynd.xlsx
+++ b/artfynd/A 25436-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110954871</v>
+        <v>110954756</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,7 +713,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571705.5223789989</v>
+        <v>571704</v>
       </c>
       <c r="R2" t="n">
-        <v>6409309.918521266</v>
+        <v>6409313</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +759,14 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>4 knoppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110954756</v>
+        <v>110954845</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -843,11 +832,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -856,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571704.3981965458</v>
+        <v>571698</v>
       </c>
       <c r="R3" t="n">
-        <v>6409313.094965842</v>
+        <v>6409320</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,24 +874,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>4 knoppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,15 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110954845</v>
+        <v>110954871</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -986,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571698.4051644339</v>
+        <v>571706</v>
       </c>
       <c r="R4" t="n">
-        <v>6409319.913818576</v>
+        <v>6409310</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,19 +984,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,12 +1017,7 @@
         <v>110954893</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571672.7715936928</v>
+        <v>571673</v>
       </c>
       <c r="R5" t="n">
-        <v>6409290.688324721</v>
+        <v>6409291</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,19 +1090,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,12 +1123,7 @@
         <v>110970579</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
